--- a/medical_surveys_questionnaires/045_medical_history_and_physical_examination_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/045_medical_history_and_physical_examination_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medical_allergies</t>
+          <t>medical_allergies_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Medical Allergies 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medical_medications</t>
+          <t>medical_medications_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Medical Medications 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Medical Conditions 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>medical_surgical_history</t>
+          <t>medical_surgical_history_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Surgical History</t>
+          <t>Medical Surgical History 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>medical_family_history</t>
+          <t>medical_family_history_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>medical_allergies_choices</t>
+          <t>medical_allergies_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medical_allergies_choices</t>
+          <t>medical_allergies_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medical_medications_choices</t>
+          <t>medical_medications_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>medical_medications_choices</t>
+          <t>medical_medications_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1528,7 +1528,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>medical_surgical_history_choices</t>
+          <t>medical_surgical_history_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>medical_surgical_history_choices</t>
+          <t>medical_surgical_history_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>medical_family_history_choices</t>
+          <t>medical_family_history_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>medical_family_history_choices</t>
+          <t>medical_family_history_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
